--- a/task184/golden/mobile_team_effect_2027.xlsx
+++ b/task184/golden/mobile_team_effect_2027.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>Passengers the mobile unit would move within the 20-minute standard, summer 2027 posting</t>
   </si>
@@ -35,39 +35,54 @@
     <t>Code</t>
   </si>
   <si>
-    <t>Host's own lanes stood down through its banks (2026)</t>
-  </si>
-  <si>
-    <t>Lanes the unit adds at the banks</t>
+    <t>Bank lanes planned and not opened</t>
+  </si>
+  <si>
+    <t>Own lanes stood down, morning bank</t>
+  </si>
+  <si>
+    <t>Own lanes stood down, evening bank</t>
   </si>
   <si>
     <t>Passengers moved, 15 Jun to 31 Aug 2027</t>
   </si>
   <si>
+    <t>Eskerford</t>
+  </si>
+  <si>
+    <t>ESK</t>
+  </si>
+  <si>
     <t>Halloran Bay</t>
   </si>
   <si>
     <t>HAL</t>
   </si>
   <si>
+    <t>Ardcarrig</t>
+  </si>
+  <si>
+    <t>ARD</t>
+  </si>
+  <si>
     <t>Cullinvale</t>
   </si>
   <si>
     <t>CUL</t>
   </si>
   <si>
-    <t>Eskerford</t>
-  </si>
-  <si>
-    <t>ESK</t>
-  </si>
-  <si>
     <t>Faranloe</t>
   </si>
   <si>
     <t>FAR</t>
   </si>
   <si>
+    <t>Glenkessan</t>
+  </si>
+  <si>
+    <t>GLK</t>
+  </si>
+  <si>
     <t>Brennagh</t>
   </si>
   <si>
@@ -80,22 +95,10 @@
     <t>DRM</t>
   </si>
   <si>
-    <t>Ardcarrig</t>
-  </si>
-  <si>
-    <t>ARD</t>
-  </si>
-  <si>
-    <t>Glenkessan</t>
-  </si>
-  <si>
-    <t>GLK</t>
-  </si>
-  <si>
-    <t>Smallest whole per cent shortfall in Halloran Bay's forecast passengers at which another posting moves more</t>
-  </si>
-  <si>
-    <t>14%</t>
+    <t>Smallest whole per cent shortfall in Eskerford's forecast passengers at which another posting moves more</t>
+  </si>
+  <si>
+    <t>13%</t>
   </si>
   <si>
     <t>Last summer at each airport</t>
@@ -119,7 +122,7 @@
     <t>Planning basis: KAS-STD-07 (2026 edition), sections 4 and 6; the design days of the summer 2027 planning sheet, each standing for every day of its period (15 to 30 June 16 days, July 31, August 31).</t>
   </si>
   <si>
-    <t>Lanes with the unit posted: the summer 2027 roster pattern, less the lanes the host's duty managers stood down in each 15 minutes of every posted day in 2026 (lane counts against the summer 2026 roster pattern), plus the unit's three lanes from 05:00 to 21:00. The summer figure is the sum of the three periods' design days times their days, rounded once.</t>
+    <t>Lanes without the unit: the lanes the checkpoint opens on its own days, the summer 2027 roster pattern less the bank lanes it does not open (2026 lane counts on the days the unit was elsewhere, against the summer 2026 roster pattern, which plans the same lanes). Lanes with the unit: those less the lanes the host's duty managers stood down in each 15 minutes of every posted day in 2026, plus the unit's three lanes from 05:00 to 21:00. The summer figure is the sum of the three periods' design days times their days, rounded once.</t>
   </si>
   <si>
     <t>Passengers screened in 2026: passenger lanes and the unit's lanes, 15 June to 31 August 2026; staff and aircrew searched at the shift changes excluded.</t>
@@ -510,27 +513,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7F9D35-4BB0-5B55-8168-ADC3363C49EF}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -546,149 +550,176 @@
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>342200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
         <v>0</v>
       </c>
-      <c r="D5" s="3">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4">
-        <v>382700</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
-        <v>237700</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="5">
+        <v>272600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>195200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>240800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
-        <v>187200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>231900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5">
-        <v>186300</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5">
+        <v>202800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5">
-        <v>184100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5">
+        <v>163700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
-        <v>180900</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>145900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
-        <v>166600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>135400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="6" t="s">
         <v>24</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -711,7 +742,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.25">
@@ -722,176 +753,176 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="5">
-        <v>616000</v>
+        <v>841500</v>
       </c>
       <c r="D4" s="7">
-        <v>112.98</v>
+        <v>98.5</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" s="7">
-        <v>8091.04</v>
+        <v>8163.34</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5">
-        <v>1299100</v>
+        <v>590000</v>
       </c>
       <c r="D5" s="7">
-        <v>116.72</v>
+        <v>112.98</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7">
-        <v>7135.92</v>
+        <v>8091.04</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5">
-        <v>890200</v>
+        <v>1051700</v>
       </c>
       <c r="D6" s="7">
-        <v>98.5</v>
+        <v>110.01</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="7">
-        <v>8163.34</v>
+        <v>7339.69</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="5">
-        <v>1058700</v>
+        <v>1215800</v>
       </c>
       <c r="D7" s="7">
-        <v>90.3</v>
+        <v>116.72</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="7">
-        <v>7991.56</v>
+        <v>7135.92</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5">
-        <v>757600</v>
+        <v>992800</v>
       </c>
       <c r="D8" s="7">
-        <v>84.7</v>
+        <v>90.3</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" s="7">
-        <v>8247.459999999999</v>
+        <v>7991.56</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5">
-        <v>866300</v>
+        <v>593300</v>
       </c>
       <c r="D9" s="7">
-        <v>95.40000000000001</v>
+        <v>93.73</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" s="7">
-        <v>8824.959999999999</v>
+        <v>8724.6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5">
-        <v>1125900</v>
+        <v>704000</v>
       </c>
       <c r="D10" s="7">
-        <v>110.01</v>
+        <v>84.7</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7">
-        <v>7339.69</v>
+        <v>8247.459999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="5">
-        <v>641000</v>
+        <v>816900</v>
       </c>
       <c r="D11" s="7">
-        <v>93.73</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" s="7">
-        <v>8724.6</v>
+        <v>8824.959999999999</v>
       </c>
     </row>
   </sheetData>
@@ -909,37 +940,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
